--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -368,7 +368,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,13 +537,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1062,7 +1055,7 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1744,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2">
         <v>10000002</v>
@@ -1821,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2">
         <v>10000003</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -179,11 +179,104 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>HeroName</t>
+  </si>
+  <si>
+    <t>HeroType</t>
+  </si>
+  <si>
+    <t>HeroHeadIcon</t>
+  </si>
+  <si>
+    <t>HeroModelID</t>
+  </si>
+  <si>
+    <t>HeroQuality</t>
+  </si>
+  <si>
+    <t>AtkDistance</t>
+  </si>
+  <si>
+    <t>AtkID</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>Act</t>
+  </si>
+  <si>
+    <t>Def</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>Cri</t>
+  </si>
+  <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>Counterattack</t>
+  </si>
+  <si>
+    <t>LifeSteal</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>ReCri</t>
+  </si>
+  <si>
+    <t>ReCombo</t>
+  </si>
+  <si>
+    <t>ReCounterattack</t>
+  </si>
+  <si>
+    <t>ReLifeSteal</t>
+  </si>
+  <si>
+    <t>ReEva</t>
+  </si>
+  <si>
+    <t>HeroDescription</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>array,int#sep=,</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>英雄名称</t>
   </si>
   <si>
@@ -254,90 +347,6 @@
   </si>
   <si>
     <t>英雄简介</t>
-  </si>
-  <si>
-    <t>HeroName</t>
-  </si>
-  <si>
-    <t>HeroType</t>
-  </si>
-  <si>
-    <t>HeroHeadIcon</t>
-  </si>
-  <si>
-    <t>HeroModelID</t>
-  </si>
-  <si>
-    <t>HeroQuality</t>
-  </si>
-  <si>
-    <t>AtkDistance</t>
-  </si>
-  <si>
-    <t>AtkID</t>
-  </si>
-  <si>
-    <t>SkillID</t>
-  </si>
-  <si>
-    <t>Act</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>Cri</t>
-  </si>
-  <si>
-    <t>Combo</t>
-  </si>
-  <si>
-    <t>Counterattack</t>
-  </si>
-  <si>
-    <t>LifeSteal</t>
-  </si>
-  <si>
-    <t>Eva</t>
-  </si>
-  <si>
-    <t>ReCri</t>
-  </si>
-  <si>
-    <t>ReCombo</t>
-  </si>
-  <si>
-    <t>ReCounterattack</t>
-  </si>
-  <si>
-    <t>ReLifeSteal</t>
-  </si>
-  <si>
-    <t>ReEva</t>
-  </si>
-  <si>
-    <t>HeroDescription</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>小战神</t>
@@ -790,9 +799,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -805,7 +812,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1396,479 +1405,486 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AA8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7"/>
+  <dimension ref="A1:Z6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="8" width="17.875" style="2"/>
-    <col min="9" max="11" width="25.625" style="2" customWidth="1"/>
-    <col min="12" max="26" width="15.625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="50.625" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="7" width="17.875" style="2"/>
+    <col min="8" max="10" width="25.625" style="2" customWidth="1"/>
+    <col min="11" max="25" width="15.625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="50.625" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="K2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="O2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>48</v>
       </c>
+      <c r="T3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:27">
-      <c r="C5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>50</v>
+    <row r="4" customHeight="1" spans="2:26">
+      <c r="B4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="K4" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" s="2">
+        <v>22</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1600</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:27">
-      <c r="C6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>53</v>
+    <row r="5" customHeight="1" spans="2:26">
+      <c r="B5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="F5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="J5" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="K5" s="2">
+        <v>120</v>
+      </c>
+      <c r="L5" s="2">
+        <v>16</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1200</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:26">
+      <c r="B6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
       </c>
       <c r="E6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="G6" s="2">
-        <v>10000001</v>
-      </c>
       <c r="H6" s="2">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="J6" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="K6" s="2">
+        <v>130</v>
+      </c>
+      <c r="L6" s="2">
+        <v>10</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1200</v>
+      </c>
+      <c r="N6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="K6" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="L6" s="2">
-        <v>100</v>
-      </c>
-      <c r="M6" s="2">
-        <v>22</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1600</v>
-      </c>
       <c r="O6" s="2">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="P6" s="2">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="R6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="S6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="T6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="U6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="V6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="W6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X6" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:27">
-      <c r="C7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="K7" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="L7" s="2">
-        <v>120</v>
-      </c>
-      <c r="M7" s="2">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2">
-        <v>1200</v>
-      </c>
-      <c r="O7" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="P7" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="T7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="U7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="W7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:27">
-      <c r="C8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8</v>
-      </c>
-      <c r="J8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="K8" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="L8" s="2">
-        <v>130</v>
-      </c>
-      <c r="M8" s="2">
-        <v>10</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1200</v>
-      </c>
-      <c r="O8" s="2">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="Q8" s="2">
         <v>0.08</v>
       </c>
-      <c r="R8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="S8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="T8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="U8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>58</v>
+      <c r="Z6" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1.战士
-2.箭手
-3.法师</t>
+1.近战
+2.远程</t>
         </r>
       </text>
     </comment>
@@ -549,12 +548,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21E5D1E-8C14-45E9-8EAE-B2A9774041BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -101,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -127,7 +120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -150,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -178,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -364,19 +357,17 @@
   </si>
   <si>
     <t>会治疗术的法师。</t>
+  </si>
+  <si>
+    <t>斧王</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,147 +395,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -558,8 +412,22 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,194 +446,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -816,256 +498,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1078,69 +518,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1398,14 +797,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Z6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -1415,7 +814,7 @@
     <col min="27" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="2" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -1575,7 +974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="3" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -1655,7 +1054,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:26">
+    <row r="4" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1732,7 +1131,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:26">
+    <row r="5" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1809,7 +1208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:26">
+    <row r="6" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1817,7 +1216,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2">
         <v>10000003</v>
@@ -1886,9 +1285,35 @@
         <v>61</v>
       </c>
     </row>
+    <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="2">
+        <v>10001001</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>10001001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1001001</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2">
+        <v>10000001</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21E5D1E-8C14-45E9-8EAE-B2A9774041BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F01BF0-A509-4C83-A09C-9834EE2A7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F01BF0-A509-4C83-A09C-9834EE2A7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -94,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -120,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +267,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>array,int#sep=,</t>
+    <t>(array#sep=,),int</t>
   </si>
   <si>
     <t>double</t>
@@ -360,14 +367,19 @@
   </si>
   <si>
     <t>斧王</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,16 +407,154 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -414,20 +564,11 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,8 +587,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -498,12 +825,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -518,28 +1087,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -797,14 +1410,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Z7"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="2"/>
@@ -814,7 +1427,7 @@
     <col min="27" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -894,7 +1507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -974,7 +1587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -1054,7 +1667,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:26">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1131,7 +1744,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:26">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1208,7 +1821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:26">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1285,7 +1898,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customHeight="1" spans="2:9">
       <c r="B7" s="2">
         <v>10001001</v>
       </c>
@@ -1312,8 +1925,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F01BF0-A509-4C83-A09C-9834EE2A7F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFEEEF97-DFBC-4FAC-BA47-20BFCF80A9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -218,148 +219,149 @@
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>Counterattack</t>
+  </si>
+  <si>
+    <t>LifeSteal</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>ReCri</t>
+  </si>
+  <si>
+    <t>ReCombo</t>
+  </si>
+  <si>
+    <t>ReCounterattack</t>
+  </si>
+  <si>
+    <t>ReLifeSteal</t>
+  </si>
+  <si>
+    <t>ReEva</t>
+  </si>
+  <si>
+    <t>HeroDescription</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>array,int#sep=,</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>英雄名称</t>
+  </si>
+  <si>
+    <t>英雄类型</t>
+  </si>
+  <si>
+    <t>英雄头像</t>
+  </si>
+  <si>
+    <t>英雄模型ID</t>
+  </si>
+  <si>
+    <t>英雄品质</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>普通攻击ID</t>
+  </si>
+  <si>
+    <t>英雄技能ID</t>
+  </si>
+  <si>
+    <t>初始攻击</t>
+  </si>
+  <si>
+    <t>初始防御</t>
+  </si>
+  <si>
+    <t>初始生命</t>
+  </si>
+  <si>
+    <t>初始攻速</t>
+  </si>
+  <si>
+    <t>初始移速</t>
+  </si>
+  <si>
+    <t>初始暴击</t>
+  </si>
+  <si>
+    <t>初始连击</t>
+  </si>
+  <si>
+    <t>初始反击</t>
+  </si>
+  <si>
+    <t>初始吸血</t>
+  </si>
+  <si>
+    <t>初始闪避</t>
+  </si>
+  <si>
+    <t>初始抗暴击</t>
+  </si>
+  <si>
+    <t>初始抗连击</t>
+  </si>
+  <si>
+    <t>初始抗反击</t>
+  </si>
+  <si>
+    <t>初始抗吸血</t>
+  </si>
+  <si>
+    <t>初始抗闪避</t>
+  </si>
+  <si>
+    <t>英雄简介</t>
+  </si>
+  <si>
+    <t>小战神</t>
+  </si>
+  <si>
+    <t>这是一个想成为大战神的战士。</t>
+  </si>
+  <si>
+    <t>神射手</t>
+  </si>
+  <si>
+    <t>百发百中的箭手。</t>
+  </si>
+  <si>
+    <t>魔法师</t>
+  </si>
+  <si>
+    <t>会治疗术的法师。</t>
+  </si>
+  <si>
+    <t>斧王</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>Cri</t>
-  </si>
-  <si>
-    <t>Combo</t>
-  </si>
-  <si>
-    <t>Counterattack</t>
-  </si>
-  <si>
-    <t>LifeSteal</t>
-  </si>
-  <si>
-    <t>Eva</t>
-  </si>
-  <si>
-    <t>ReCri</t>
-  </si>
-  <si>
-    <t>ReCombo</t>
-  </si>
-  <si>
-    <t>ReCounterattack</t>
-  </si>
-  <si>
-    <t>ReLifeSteal</t>
-  </si>
-  <si>
-    <t>ReEva</t>
-  </si>
-  <si>
-    <t>HeroDescription</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>array,int#sep=,</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>英雄名称</t>
-  </si>
-  <si>
-    <t>英雄类型</t>
-  </si>
-  <si>
-    <t>英雄头像</t>
-  </si>
-  <si>
-    <t>英雄模型ID</t>
-  </si>
-  <si>
-    <t>英雄品质</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
-  </si>
-  <si>
-    <t>普通攻击ID</t>
-  </si>
-  <si>
-    <t>英雄技能ID</t>
-  </si>
-  <si>
-    <t>初始攻击</t>
-  </si>
-  <si>
-    <t>初始防御</t>
-  </si>
-  <si>
-    <t>初始生命</t>
-  </si>
-  <si>
-    <t>初始攻速</t>
-  </si>
-  <si>
-    <t>初始移速</t>
-  </si>
-  <si>
-    <t>初始暴击</t>
-  </si>
-  <si>
-    <t>初始连击</t>
-  </si>
-  <si>
-    <t>初始反击</t>
-  </si>
-  <si>
-    <t>初始吸血</t>
-  </si>
-  <si>
-    <t>初始闪避</t>
-  </si>
-  <si>
-    <t>初始抗暴击</t>
-  </si>
-  <si>
-    <t>初始抗连击</t>
-  </si>
-  <si>
-    <t>初始抗反击</t>
-  </si>
-  <si>
-    <t>初始抗吸血</t>
-  </si>
-  <si>
-    <t>初始抗闪避</t>
-  </si>
-  <si>
-    <t>英雄简介</t>
-  </si>
-  <si>
-    <t>小战神</t>
-  </si>
-  <si>
-    <t>这是一个想成为大战神的战士。</t>
-  </si>
-  <si>
-    <t>神射手</t>
-  </si>
-  <si>
-    <t>百发百中的箭手。</t>
-  </si>
-  <si>
-    <t>魔法师</t>
-  </si>
-  <si>
-    <t>会治疗术的法师。</t>
-  </si>
-  <si>
-    <t>斧王</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -367,7 +369,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,6 +424,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -505,7 +514,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -525,6 +534,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -860,198 +872,198 @@
       <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1059,7 +1071,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1128,7 +1140,7 @@
         <v>0.02</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1136,7 +1148,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -1205,7 +1217,7 @@
         <v>0.03</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1213,7 +1225,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
@@ -1282,7 +1294,7 @@
         <v>0.08</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1290,7 +1302,7 @@
         <v>10001001</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206D80DE-C26F-4758-99C8-A9C471E149C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E7FDA-49C2-45EC-B636-54AE60C62C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E7FDA-49C2-45EC-B636-54AE60C62C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF1439D-FE41-499A-8685-D7162DF0FE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1161,10 +1161,10 @@
         <v>45</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>45</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF1439D-FE41-499A-8685-D7162DF0FE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -50,15 +55,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{EF3466D7-A140-4197-A616-3B35D178AD64}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -66,9 +69,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -78,14 +79,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -94,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,14 +102,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -119,7 +117,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -128,14 +125,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -144,7 +140,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,15 +151,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{F9A8AA80-2A06-4904-BEDD-53512E74718D}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -172,9 +165,7 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -183,14 +174,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -199,7 +189,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -208,14 +197,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -224,7 +212,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -238,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -249,6 +236,12 @@
     <t>HeroName</t>
   </si>
   <si>
+    <t>AtkType</t>
+  </si>
+  <si>
+    <t>HeroType</t>
+  </si>
+  <si>
     <t>HeroHeadIcon</t>
   </si>
   <si>
@@ -258,13 +251,61 @@
     <t>HeroQuality</t>
   </si>
   <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>AtkID</t>
+  </si>
+  <si>
+    <t>SkillID</t>
+  </si>
+  <si>
+    <t>Base_Hp</t>
+  </si>
+  <si>
+    <t>Base_Act</t>
+  </si>
+  <si>
+    <t>Base_Def</t>
+  </si>
+  <si>
+    <t>Base_Adf</t>
+  </si>
+  <si>
+    <t>Base_Cri</t>
+  </si>
+  <si>
+    <t>Base_ReCri</t>
+  </si>
+  <si>
+    <t>Base_Eva</t>
+  </si>
+  <si>
+    <t>Base_Hit</t>
+  </si>
+  <si>
+    <t>Base_HitLess</t>
+  </si>
+  <si>
+    <t>Base_MoveSpeed</t>
+  </si>
+  <si>
+    <t>Base_AtkSpeed</t>
+  </si>
+  <si>
     <t>AtkDistance</t>
   </si>
   <si>
-    <t>AtkID</t>
-  </si>
-  <si>
-    <t>SkillID</t>
+    <t>Lv_Hp</t>
+  </si>
+  <si>
+    <t>Lv_Act</t>
+  </si>
+  <si>
+    <t>Lv_Def</t>
+  </si>
+  <si>
+    <t>Lv_Adf</t>
   </si>
   <si>
     <t>HeroDescription</t>
@@ -291,6 +332,12 @@
     <t>英雄名称</t>
   </si>
   <si>
+    <t>攻击类型</t>
+  </si>
+  <si>
+    <t>英雄标签</t>
+  </si>
+  <si>
     <t>英雄头像</t>
   </si>
   <si>
@@ -300,13 +347,61 @@
     <t>英雄品质</t>
   </si>
   <si>
+    <t>伤害类型</t>
+  </si>
+  <si>
+    <t>普通攻击ID</t>
+  </si>
+  <si>
+    <t>英雄技能ID</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>物防</t>
+  </si>
+  <si>
+    <t>魔防</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>抗暴</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>伤害减免</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>攻击速度</t>
+  </si>
+  <si>
     <t>攻击距离</t>
   </si>
   <si>
-    <t>普通攻击ID</t>
-  </si>
-  <si>
-    <t>英雄技能ID</t>
+    <t>等级成长血量</t>
+  </si>
+  <si>
+    <t>等级成长攻击</t>
+  </si>
+  <si>
+    <t>等级成长物防</t>
+  </si>
+  <si>
+    <t>等级成长魔防</t>
   </si>
   <si>
     <t>英雄简介</t>
@@ -315,231 +410,68 @@
     <t>斧王</t>
   </si>
   <si>
-    <t>血量</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Hp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Act</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>物防</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔防</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Def</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Adf</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Cri</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>抗暴</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_ReCri</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪避</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Eva</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_Hit</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害减免</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_HitLess</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_MoveSpeed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base_AtkSpeed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级成长血量</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级成长攻击</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级成长物防</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级成长魔防</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>20000001,30000001,30000002,30000003</t>
   </si>
   <si>
     <t>一个拿着斧头的强壮家伙。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000001,30000001,30000002,30000003</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv_Hp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv_Act</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv_Def</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv_Adf</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>流浪剑客</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害类型</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000002,30000004,30000005,30000006</t>
+  </si>
+  <si>
+    <t>在外面流浪的无名剑客。</t>
   </si>
   <si>
     <t>剑圣</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000003,30000007,30000008,30000009</t>
+  </si>
+  <si>
+    <t>剑术出神入化的大师。</t>
   </si>
   <si>
     <t>全能骑士</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄标签</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击类型</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeroType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000005,30000013,30000014,30000015</t>
+  </si>
+  <si>
+    <t>一个打辅助的骑士。</t>
   </si>
   <si>
     <t>冰女</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000004,30000010,30000011,30000012</t>
+  </si>
+  <si>
+    <t>冰冷的法师。</t>
   </si>
   <si>
     <t>术士</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000002,30000004,30000005,30000006</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000003,30000007,30000008,30000009</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000004,30000010,30000011,30000012</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000005,30000013,30000014,30000015</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>20000006,30000016,30000017,30000018</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>在外面流浪的无名剑客。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑术出神入化的大师。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>一个打辅助的骑士。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冷的法师。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>治疗队友的巫师。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,7 +483,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -559,68 +490,178 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -639,8 +680,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -691,14 +918,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -711,31 +1180,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -993,14 +1503,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="9" width="17.875" style="2"/>
@@ -1013,7 +1523,7 @@
     <col min="29" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,259 +1534,259 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:28">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
+      <c r="C4" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1299,8 +1809,8 @@
       <c r="J4" s="2">
         <v>10000001</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>54</v>
+      <c r="K4" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="L4" s="2">
         <v>1400</v>
@@ -1351,15 +1861,15 @@
         <v>20</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:28">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1382,8 +1892,8 @@
       <c r="J5" s="2">
         <v>10000001</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>70</v>
+      <c r="K5" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="L5" s="2">
         <v>800</v>
@@ -1434,15 +1944,15 @@
         <v>10</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:28">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1465,8 +1975,8 @@
       <c r="J6" s="2">
         <v>10000001</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>71</v>
+      <c r="K6" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="L6" s="2">
         <v>800</v>
@@ -1517,15 +2027,15 @@
         <v>10</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customHeight="1" spans="2:28">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1548,8 +2058,8 @@
       <c r="J7" s="2">
         <v>10000001</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>73</v>
+      <c r="K7" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="L7" s="2">
         <v>1000</v>
@@ -1600,15 +2110,15 @@
         <v>15</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" customHeight="1" spans="2:28">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -1631,8 +2141,8 @@
       <c r="J8" s="2">
         <v>10000002</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>72</v>
+      <c r="K8" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="L8" s="2">
         <v>800</v>
@@ -1683,15 +2193,15 @@
         <v>10</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" customHeight="1" spans="2:28">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -1714,8 +2224,8 @@
       <c r="J9" s="2">
         <v>10000003</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>74</v>
+      <c r="K9" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="L9" s="2">
         <v>1000</v>
@@ -1766,12 +2276,12 @@
         <v>15</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\miniprogram_1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C935D933-989A-425B-8D76-A6C0878CE294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -102,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -125,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -151,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -174,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -225,7 +218,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -459,19 +452,17 @@
   </si>
   <si>
     <t>治疗队友的巫师。</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -499,150 +490,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -660,8 +507,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,194 +540,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -918,256 +592,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1180,72 +612,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1503,14 +894,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="9" width="17.875" style="2"/>
@@ -1523,7 +914,7 @@
     <col min="29" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1000,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1628,8 +1019,8 @@
       <c r="F2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>29</v>
+      <c r="G2" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>29</v>
@@ -1695,7 +1086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1781,7 +1172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:28">
+    <row r="4" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
@@ -1864,7 +1255,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:28">
+    <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
@@ -1947,7 +1338,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:28">
+    <row r="6" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
@@ -2030,7 +1421,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:28">
+    <row r="7" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
@@ -2113,7 +1504,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:28">
+    <row r="8" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
@@ -2196,7 +1587,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:28">
+    <row r="9" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
@@ -2280,8 +1671,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\miniprogram_1\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C935D933-989A-425B-8D76-A6C0878CE294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -72,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -95,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -144,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -167,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -241,7 +248,7 @@
     <t>HeroModelID</t>
   </si>
   <si>
-    <t>HeroQuality</t>
+    <t>HeroUpStarNeed</t>
   </si>
   <si>
     <t>DamageType</t>
@@ -337,7 +344,7 @@
     <t>英雄模型ID</t>
   </si>
   <si>
-    <t>英雄品质</t>
+    <t>英雄升星需要的魂石</t>
   </si>
   <si>
     <t>伤害类型</t>
@@ -403,6 +410,9 @@
     <t>斧王</t>
   </si>
   <si>
+    <t>400,500,600,700,800</t>
+  </si>
+  <si>
     <t>20000001,30000001,30000002,30000003</t>
   </si>
   <si>
@@ -452,17 +462,19 @@
   </si>
   <si>
     <t>治疗队友的巫师。</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,10 +502,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -507,21 +656,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -540,8 +676,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -592,14 +914,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -612,31 +1176,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -894,17 +1499,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AB9"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="9" width="17.875" style="2"/>
+    <col min="2" max="7" width="17.875" style="2"/>
+    <col min="8" max="8" width="27.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.875" style="2"/>
     <col min="10" max="10" width="25.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="35.625" style="2" customWidth="1"/>
     <col min="12" max="22" width="15.625" style="2" customWidth="1"/>
@@ -914,7 +1521,7 @@
     <col min="29" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1607,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1019,11 +1626,11 @@
       <c r="F2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>78</v>
+      <c r="G2" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>29</v>
@@ -1086,7 +1693,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1172,7 +1779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" customHeight="1" spans="2:28">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
@@ -1191,8 +1798,8 @@
       <c r="G4" s="2">
         <v>10001001</v>
       </c>
-      <c r="H4" s="2">
-        <v>3</v>
+      <c r="H4" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1201,7 +1808,7 @@
         <v>10000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L4" s="2">
         <v>1400</v>
@@ -1252,15 +1859,15 @@
         <v>20</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" customHeight="1" spans="2:28">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1274,8 +1881,8 @@
       <c r="G5" s="2">
         <v>10001002</v>
       </c>
-      <c r="H5" s="2">
-        <v>4</v>
+      <c r="H5" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1284,7 +1891,7 @@
         <v>10000001</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L5" s="2">
         <v>800</v>
@@ -1335,15 +1942,15 @@
         <v>10</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" customHeight="1" spans="2:28">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1357,8 +1964,8 @@
       <c r="G6" s="2">
         <v>10001003</v>
       </c>
-      <c r="H6" s="2">
-        <v>5</v>
+      <c r="H6" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1367,7 +1974,7 @@
         <v>10000001</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" s="2">
         <v>800</v>
@@ -1418,15 +2025,15 @@
         <v>10</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" customHeight="1" spans="2:28">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1440,8 +2047,8 @@
       <c r="G7" s="2">
         <v>10001004</v>
       </c>
-      <c r="H7" s="2">
-        <v>1</v>
+      <c r="H7" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -1450,7 +2057,7 @@
         <v>10000001</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L7" s="2">
         <v>1000</v>
@@ -1501,15 +2108,15 @@
         <v>15</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" customHeight="1" spans="2:28">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -1523,8 +2130,8 @@
       <c r="G8" s="2">
         <v>10002001</v>
       </c>
-      <c r="H8" s="2">
-        <v>2</v>
+      <c r="H8" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
@@ -1533,7 +2140,7 @@
         <v>10000002</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L8" s="2">
         <v>800</v>
@@ -1584,15 +2191,15 @@
         <v>10</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" customHeight="1" spans="2:28">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -1606,8 +2213,8 @@
       <c r="G9" s="2">
         <v>10002002</v>
       </c>
-      <c r="H9" s="2">
-        <v>3</v>
+      <c r="H9" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -1616,7 +2223,7 @@
         <v>10000003</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L9" s="2">
         <v>1000</v>
@@ -1667,12 +2274,12 @@
         <v>15</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,32 +122,6 @@
           <t xml:space="preserve">
 资源位置在
 Assets\Bundles\Unit\Hero</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1.白
-2.绿
-3.蓝
-4.紫
-5.橙</t>
         </r>
       </text>
     </comment>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -210,12 +210,12 @@
     <t>HeroName</t>
   </si>
   <si>
-    <t>AtkType</t>
-  </si>
-  <si>
     <t>HeroType</t>
   </si>
   <si>
+    <t>HeroTag</t>
+  </si>
+  <si>
     <t>HeroHeadIcon</t>
   </si>
   <si>
@@ -306,7 +306,7 @@
     <t>英雄名称</t>
   </si>
   <si>
-    <t>攻击类型</t>
+    <t>英雄类型</t>
   </si>
   <si>
     <t>英雄标签</t>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -297,7 +297,7 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
-    <t>double</t>
+    <t>long</t>
   </si>
   <si>
     <t>##</t>
@@ -620,12 +620,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1797,13 +1797,13 @@
         <v>50</v>
       </c>
       <c r="P4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q4" s="2">
         <v>0</v>
       </c>
       <c r="R4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S4" s="2">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="U4" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V4" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W4" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="X4" s="2">
         <v>150</v>
@@ -1880,13 +1880,13 @@
         <v>30</v>
       </c>
       <c r="P5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
       </c>
       <c r="R5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
@@ -1895,13 +1895,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V5" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W5" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="X5" s="2">
         <v>100</v>
@@ -1963,13 +1963,13 @@
         <v>30</v>
       </c>
       <c r="P6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q6" s="2">
         <v>0</v>
       </c>
       <c r="R6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S6" s="2">
         <v>0</v>
@@ -1978,13 +1978,13 @@
         <v>0</v>
       </c>
       <c r="U6" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V6" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W6" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="X6" s="2">
         <v>100</v>
@@ -2046,13 +2046,13 @@
         <v>40</v>
       </c>
       <c r="P7" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q7" s="2">
         <v>0</v>
       </c>
       <c r="R7" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -2061,13 +2061,13 @@
         <v>0</v>
       </c>
       <c r="U7" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V7" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W7" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="X7" s="2">
         <v>120</v>
@@ -2129,13 +2129,13 @@
         <v>30</v>
       </c>
       <c r="P8" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q8" s="2">
         <v>0</v>
       </c>
       <c r="R8" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S8" s="2">
         <v>0</v>
@@ -2144,13 +2144,13 @@
         <v>0</v>
       </c>
       <c r="U8" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V8" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W8" s="2">
-        <v>6</v>
+        <v>20000</v>
       </c>
       <c r="X8" s="2">
         <v>100</v>
@@ -2212,13 +2212,13 @@
         <v>40</v>
       </c>
       <c r="P9" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
       </c>
       <c r="R9" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
@@ -2227,13 +2227,13 @@
         <v>0</v>
       </c>
       <c r="U9" s="2">
-        <v>6</v>
+        <v>60000</v>
       </c>
       <c r="V9" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="W9" s="2">
-        <v>6</v>
+        <v>20000</v>
       </c>
       <c r="X9" s="2">
         <v>120</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -620,12 +620,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1785,7 +1785,7 @@
         <v>62</v>
       </c>
       <c r="L4" s="2">
-        <v>1400</v>
+        <v>14000</v>
       </c>
       <c r="M4" s="2">
         <v>60</v>
@@ -1868,7 +1868,7 @@
         <v>65</v>
       </c>
       <c r="L5" s="2">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="M5" s="2">
         <v>100</v>
@@ -1951,7 +1951,7 @@
         <v>68</v>
       </c>
       <c r="L6" s="2">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="M6" s="2">
         <v>100</v>
@@ -2034,7 +2034,7 @@
         <v>71</v>
       </c>
       <c r="L7" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="M7" s="2">
         <v>80</v>
@@ -2117,7 +2117,7 @@
         <v>74</v>
       </c>
       <c r="L8" s="2">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="M8" s="2">
         <v>100</v>
@@ -2200,7 +2200,7 @@
         <v>77</v>
       </c>
       <c r="L9" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="2">
         <v>80</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -2150,7 +2150,7 @@
         <v>10000</v>
       </c>
       <c r="W8" s="2">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="X8" s="2">
         <v>100</v>
@@ -2233,7 +2233,7 @@
         <v>10000</v>
       </c>
       <c r="W9" s="2">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="X9" s="2">
         <v>120</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -240,6 +240,9 @@
     <t>Base_Act</t>
   </si>
   <si>
+    <t>Base_Mage</t>
+  </si>
+  <si>
     <t>Base_Def</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
   </si>
   <si>
     <t>攻击</t>
+  </si>
+  <si>
+    <t>法强</t>
   </si>
   <si>
     <t>物防</t>
@@ -1479,7 +1485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1488,14 +1494,14 @@
     <col min="9" max="9" width="17.875" style="2"/>
     <col min="10" max="10" width="25.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="35.625" style="2" customWidth="1"/>
-    <col min="12" max="22" width="15.625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="25.625" style="2" customWidth="1"/>
-    <col min="24" max="27" width="15.625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="50.625" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="17.875" style="2"/>
+    <col min="12" max="23" width="15.625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="25.625" style="2" customWidth="1"/>
+    <col min="25" max="28" width="15.625" style="2" customWidth="1"/>
+    <col min="29" max="29" width="50.625" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,185 +1586,194 @@
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB2" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="AC2" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:28">
+    <row r="4" customHeight="1" spans="2:29">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1773,7 +1788,7 @@
         <v>10001001</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1782,7 +1797,7 @@
         <v>10000001</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L4" s="2">
         <v>14000</v>
@@ -1791,57 +1806,60 @@
         <v>60</v>
       </c>
       <c r="N4" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O4" s="2">
         <v>50</v>
       </c>
       <c r="P4" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="2">
         <v>500</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>500</v>
-      </c>
-      <c r="S4" s="2">
-        <v>0</v>
       </c>
       <c r="T4" s="2">
         <v>0</v>
       </c>
       <c r="U4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2">
         <v>60000</v>
       </c>
-      <c r="V4" s="2">
+      <c r="W4" s="2">
         <v>10000</v>
       </c>
-      <c r="W4" s="2">
+      <c r="X4" s="2">
         <v>20000</v>
       </c>
-      <c r="X4" s="2">
+      <c r="Y4" s="2">
         <v>150</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Z4" s="2">
         <v>10</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>20</v>
       </c>
       <c r="AA4" s="2">
         <v>20</v>
       </c>
-      <c r="AB4" s="2" t="s">
-        <v>63</v>
+      <c r="AB4" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:28">
+    <row r="5" customHeight="1" spans="2:29">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1856,7 +1874,7 @@
         <v>10001002</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1865,7 +1883,7 @@
         <v>10000001</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L5" s="2">
         <v>8000</v>
@@ -1874,57 +1892,60 @@
         <v>100</v>
       </c>
       <c r="N5" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O5" s="2">
         <v>30</v>
       </c>
       <c r="P5" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="2">
         <v>500</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>500</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0</v>
       </c>
       <c r="T5" s="2">
         <v>0</v>
       </c>
       <c r="U5" s="2">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2">
         <v>60000</v>
       </c>
-      <c r="V5" s="2">
+      <c r="W5" s="2">
         <v>10000</v>
       </c>
-      <c r="W5" s="2">
+      <c r="X5" s="2">
         <v>20000</v>
       </c>
-      <c r="X5" s="2">
+      <c r="Y5" s="2">
         <v>100</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Z5" s="2">
         <v>20</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>10</v>
       </c>
       <c r="AA5" s="2">
         <v>10</v>
       </c>
-      <c r="AB5" s="2" t="s">
-        <v>66</v>
+      <c r="AB5" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:28">
+    <row r="6" customHeight="1" spans="2:29">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1939,7 +1960,7 @@
         <v>10001003</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1948,7 +1969,7 @@
         <v>10000001</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L6" s="2">
         <v>8000</v>
@@ -1957,57 +1978,60 @@
         <v>100</v>
       </c>
       <c r="N6" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O6" s="2">
         <v>30</v>
       </c>
       <c r="P6" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="2">
         <v>500</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>500</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
       </c>
       <c r="T6" s="2">
         <v>0</v>
       </c>
       <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
         <v>60000</v>
       </c>
-      <c r="V6" s="2">
+      <c r="W6" s="2">
         <v>10000</v>
       </c>
-      <c r="W6" s="2">
+      <c r="X6" s="2">
         <v>20000</v>
       </c>
-      <c r="X6" s="2">
+      <c r="Y6" s="2">
         <v>100</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Z6" s="2">
         <v>20</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>10</v>
       </c>
       <c r="AA6" s="2">
         <v>10</v>
       </c>
-      <c r="AB6" s="2" t="s">
-        <v>69</v>
+      <c r="AB6" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:28">
+    <row r="7" customHeight="1" spans="2:29">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2022,7 +2046,7 @@
         <v>10001004</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -2031,7 +2055,7 @@
         <v>10000001</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L7" s="2">
         <v>10000</v>
@@ -2040,40 +2064,40 @@
         <v>80</v>
       </c>
       <c r="N7" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="O7" s="2">
         <v>40</v>
       </c>
       <c r="P7" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="2">
         <v>500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>0</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>500</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
       <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
         <v>60000</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>10000</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>20000</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>120</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>15</v>
       </c>
       <c r="Z7" s="2">
         <v>15</v>
@@ -2081,16 +2105,19 @@
       <c r="AA7" s="2">
         <v>15</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>72</v>
+      <c r="AB7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:28">
+    <row r="8" customHeight="1" spans="2:29">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2105,7 +2132,7 @@
         <v>10002001</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
@@ -2114,7 +2141,7 @@
         <v>10000002</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="2">
         <v>8000</v>
@@ -2123,57 +2150,60 @@
         <v>100</v>
       </c>
       <c r="N8" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O8" s="2">
         <v>30</v>
       </c>
       <c r="P8" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="2">
         <v>500</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>500</v>
-      </c>
-      <c r="S8" s="2">
-        <v>0</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
       <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
         <v>60000</v>
       </c>
-      <c r="V8" s="2">
+      <c r="W8" s="2">
         <v>10000</v>
       </c>
-      <c r="W8" s="2">
+      <c r="X8" s="2">
         <v>80000</v>
       </c>
-      <c r="X8" s="2">
+      <c r="Y8" s="2">
         <v>100</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Z8" s="2">
         <v>20</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>10</v>
       </c>
       <c r="AA8" s="2">
         <v>10</v>
       </c>
-      <c r="AB8" s="2" t="s">
-        <v>75</v>
+      <c r="AB8" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:28">
+    <row r="9" customHeight="1" spans="2:29">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2188,7 +2218,7 @@
         <v>10002002</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -2197,7 +2227,7 @@
         <v>10000003</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L9" s="2">
         <v>10000</v>
@@ -2206,40 +2236,40 @@
         <v>80</v>
       </c>
       <c r="N9" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="O9" s="2">
         <v>40</v>
       </c>
       <c r="P9" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="2">
         <v>500</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>500</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
       </c>
       <c r="T9" s="2">
         <v>0</v>
       </c>
       <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
         <v>60000</v>
       </c>
-      <c r="V9" s="2">
+      <c r="W9" s="2">
         <v>10000</v>
       </c>
-      <c r="W9" s="2">
+      <c r="X9" s="2">
         <v>80000</v>
       </c>
-      <c r="X9" s="2">
+      <c r="Y9" s="2">
         <v>120</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>15</v>
       </c>
       <c r="Z9" s="2">
         <v>15</v>
@@ -2247,8 +2277,11 @@
       <c r="AA9" s="2">
         <v>15</v>
       </c>
-      <c r="AB9" s="2" t="s">
-        <v>78</v>
+      <c r="AB9" s="2">
+        <v>15</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -626,12 +626,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -228,10 +228,10 @@
     <t>DamageType</t>
   </si>
   <si>
-    <t>AtkID</t>
-  </si>
-  <si>
-    <t>SkillID</t>
+    <t>AtkId</t>
+  </si>
+  <si>
+    <t>UnlockSkillInfos</t>
   </si>
   <si>
     <t>Base_Hp</t>
@@ -300,6 +300,9 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
+    <t>(array#sep=@),UnlockSkillInfo</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -393,7 +396,7 @@
     <t>400,500,600,700,800</t>
   </si>
   <si>
-    <t>20000001,30000001,30000002,30000003</t>
+    <t>0;20000001@1;30000001@2;30000002@3;30000003</t>
   </si>
   <si>
     <t>一个拿着斧头的强壮家伙。</t>
@@ -402,7 +405,7 @@
     <t>流浪剑客</t>
   </si>
   <si>
-    <t>20000002,30000004,30000005,30000006</t>
+    <t>0;20000002@1;30000004@2;30000005@3;30000006</t>
   </si>
   <si>
     <t>在外面流浪的无名剑客。</t>
@@ -411,7 +414,7 @@
     <t>剑圣</t>
   </si>
   <si>
-    <t>20000003,30000007,30000008,30000009</t>
+    <t>0;20000003@1;30000007@2;30000008@3;30000009</t>
   </si>
   <si>
     <t>剑术出神入化的大师。</t>
@@ -420,7 +423,7 @@
     <t>全能骑士</t>
   </si>
   <si>
-    <t>20000005,30000013,30000014,30000015</t>
+    <t>0;20000005@1;30000013@2;30000014@3;30000015</t>
   </si>
   <si>
     <t>一个打辅助的骑士。</t>
@@ -429,7 +432,7 @@
     <t>冰女</t>
   </si>
   <si>
-    <t>20000004,30000010,30000011,30000012</t>
+    <t>0;20000004@1;30000010@2;30000011@3;30000012</t>
   </si>
   <si>
     <t>冰冷的法师。</t>
@@ -438,7 +441,7 @@
     <t>术士</t>
   </si>
   <si>
-    <t>20000006,30000016,30000017,30000018</t>
+    <t>0;20000006@1;30000016@2;30000017@3;30000018</t>
   </si>
   <si>
     <t>治疗队友的巫师。</t>
@@ -1143,26 +1146,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1493,7 +1493,7 @@
     <col min="8" max="8" width="27.25" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.875" style="2"/>
     <col min="10" max="10" width="25.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="35.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="61.25" style="2" customWidth="1"/>
     <col min="12" max="23" width="15.625" style="2" customWidth="1"/>
     <col min="24" max="24" width="25.625" style="2" customWidth="1"/>
     <col min="25" max="28" width="15.625" style="2" customWidth="1"/>
@@ -1622,7 +1622,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>30</v>
@@ -1640,28 +1640,28 @@
         <v>30</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>30</v>
@@ -1681,91 +1681,91 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC3" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:29">
@@ -1773,7 +1773,7 @@
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1787,8 +1787,8 @@
       <c r="G4" s="2">
         <v>10001001</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>63</v>
+      <c r="H4" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1796,8 +1796,8 @@
       <c r="J4" s="2">
         <v>10000001</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>64</v>
+      <c r="K4" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="L4" s="2">
         <v>14000</v>
@@ -1851,7 +1851,7 @@
         <v>20</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:29">
@@ -1859,7 +1859,7 @@
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1873,8 +1873,8 @@
       <c r="G5" s="2">
         <v>10001002</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>63</v>
+      <c r="H5" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1882,8 +1882,8 @@
       <c r="J5" s="2">
         <v>10000001</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>67</v>
+      <c r="K5" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="L5" s="2">
         <v>8000</v>
@@ -1937,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:29">
@@ -1945,7 +1945,7 @@
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1959,8 +1959,8 @@
       <c r="G6" s="2">
         <v>10001003</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>63</v>
+      <c r="H6" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1968,8 +1968,8 @@
       <c r="J6" s="2">
         <v>10000001</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>70</v>
+      <c r="K6" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="L6" s="2">
         <v>8000</v>
@@ -2023,7 +2023,7 @@
         <v>10</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:29">
@@ -2031,7 +2031,7 @@
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2045,8 +2045,8 @@
       <c r="G7" s="2">
         <v>10001004</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>63</v>
+      <c r="H7" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
@@ -2054,8 +2054,8 @@
       <c r="J7" s="2">
         <v>10000001</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>73</v>
+      <c r="K7" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="L7" s="2">
         <v>10000</v>
@@ -2109,7 +2109,7 @@
         <v>15</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:29">
@@ -2117,7 +2117,7 @@
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2131,8 +2131,8 @@
       <c r="G8" s="2">
         <v>10002001</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>63</v>
+      <c r="H8" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
@@ -2140,8 +2140,8 @@
       <c r="J8" s="2">
         <v>10000002</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>76</v>
+      <c r="K8" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="L8" s="2">
         <v>8000</v>
@@ -2195,7 +2195,7 @@
         <v>10</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:29">
@@ -2203,7 +2203,7 @@
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2217,8 +2217,8 @@
       <c r="G9" s="2">
         <v>10002002</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>63</v>
+      <c r="H9" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -2226,8 +2226,8 @@
       <c r="J9" s="2">
         <v>10000003</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>79</v>
+      <c r="K9" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="L9" s="2">
         <v>10000</v>
@@ -2281,7 +2281,7 @@
         <v>15</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -396,7 +396,7 @@
     <t>400,500,600,700,800</t>
   </si>
   <si>
-    <t>0;20000001@1;30000001@2;30000002@3;30000003</t>
+    <t>0;20000001@1;30000001@3;30000002@5;30000003</t>
   </si>
   <si>
     <t>一个拿着斧头的强壮家伙。</t>
@@ -405,7 +405,7 @@
     <t>流浪剑客</t>
   </si>
   <si>
-    <t>0;20000002@1;30000004@2;30000005@3;30000006</t>
+    <t>0;20000002@1;30000004@3;30000005@5;30000006</t>
   </si>
   <si>
     <t>在外面流浪的无名剑客。</t>
@@ -414,7 +414,7 @@
     <t>剑圣</t>
   </si>
   <si>
-    <t>0;20000003@1;30000007@2;30000008@3;30000009</t>
+    <t>0;20000003@1;30000007@3;30000008@5;30000009</t>
   </si>
   <si>
     <t>剑术出神入化的大师。</t>
@@ -423,7 +423,7 @@
     <t>全能骑士</t>
   </si>
   <si>
-    <t>0;20000005@1;30000013@2;30000014@3;30000015</t>
+    <t>0;20000005@1;30000013@3;30000014@5;30000015</t>
   </si>
   <si>
     <t>一个打辅助的骑士。</t>
@@ -432,7 +432,7 @@
     <t>冰女</t>
   </si>
   <si>
-    <t>0;20000004@1;30000010@2;30000011@3;30000012</t>
+    <t>0;20000004@1;30000010@3;30000011@5;30000012</t>
   </si>
   <si>
     <t>冰冷的法师。</t>
@@ -441,7 +441,7 @@
     <t>术士</t>
   </si>
   <si>
-    <t>0;20000006@1;30000016@2;30000017@3;30000018</t>
+    <t>0;20000006@1;30000016@3;30000017@5;30000018</t>
   </si>
   <si>
     <t>治疗队友的巫师。</t>
@@ -629,12 +629,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1768,7 +1768,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:29">
+    <row r="4" customHeight="1" spans="1:29">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:29">
+    <row r="5" customHeight="1" spans="1:29">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:29">
+    <row r="6" customHeight="1" spans="1:29">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:29">
+    <row r="7" customHeight="1" spans="1:29">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:29">
+    <row r="8" customHeight="1" spans="1:29">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:29">
+    <row r="9" customHeight="1" spans="1:29">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -393,7 +393,7 @@
     <t>斧王</t>
   </si>
   <si>
-    <t>400,500,600,700,800</t>
+    <t>400,500,600,700,800,900</t>
   </si>
   <si>
     <t>0;20000001@1;30000001@3;30000002@5;30000003</t>
@@ -1768,7 +1768,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:29">
+    <row r="4" customHeight="1" spans="2:29">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:29">
+    <row r="5" customHeight="1" spans="2:29">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:29">
+    <row r="6" customHeight="1" spans="2:29">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:29">
+    <row r="7" customHeight="1" spans="2:29">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:29">
+    <row r="8" customHeight="1" spans="2:29">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:29">
+    <row r="9" customHeight="1" spans="2:29">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -629,12 +629,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1146,7 +1146,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1163,6 +1163,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1768,7 +1771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:29">
+    <row r="4" customHeight="1" spans="1:29">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
@@ -1814,7 +1817,7 @@
       <c r="P4" s="2">
         <v>50</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="6">
         <v>500</v>
       </c>
       <c r="R4" s="2">
@@ -1854,7 +1857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:29">
+    <row r="5" customHeight="1" spans="1:29">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:29">
+    <row r="6" customHeight="1" spans="1:29">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:29">
+    <row r="7" customHeight="1" spans="1:29">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
@@ -2112,7 +2115,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:29">
+    <row r="8" customHeight="1" spans="1:29">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:29">
+    <row r="9" customHeight="1" spans="1:29">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
@@ -2244,8 +2247,8 @@
       <c r="P9" s="2">
         <v>40</v>
       </c>
-      <c r="Q9" s="2">
-        <v>500</v>
+      <c r="Q9" s="6">
+        <v>1000000</v>
       </c>
       <c r="R9" s="2">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -97,12 +97,39 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+1.绿
+2.蓝
+3.黄
+4.橙
+5.紫
+6.红</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 资源位置在
 Assets\Bundles\Icon\HeroIcon</t>
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -125,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -148,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -171,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +226,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -216,6 +243,12 @@
     <t>HeroTag</t>
   </si>
   <si>
+    <t>HeroQuality</t>
+  </si>
+  <si>
+    <t>RecycleItem</t>
+  </si>
+  <si>
     <t>HeroHeadIcon</t>
   </si>
   <si>
@@ -297,6 +330,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=@),rewardItem</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -318,6 +354,12 @@
     <t>英雄标签</t>
   </si>
   <si>
+    <t>英雄品质</t>
+  </si>
+  <si>
+    <t>分解奖励</t>
+  </si>
+  <si>
     <t>英雄头像</t>
   </si>
   <si>
@@ -393,6 +435,9 @@
     <t>斧王</t>
   </si>
   <si>
+    <t>10002001;10</t>
+  </si>
+  <si>
     <t>400,500,600,700,800,900</t>
   </si>
   <si>
@@ -405,6 +450,9 @@
     <t>流浪剑客</t>
   </si>
   <si>
+    <t>10002002;10</t>
+  </si>
+  <si>
     <t>0;20000002@1;30000004@3;30000005@5;30000006</t>
   </si>
   <si>
@@ -414,6 +462,9 @@
     <t>剑圣</t>
   </si>
   <si>
+    <t>10002003;10</t>
+  </si>
+  <si>
     <t>0;20000003@1;30000007@3;30000008@5;30000009</t>
   </si>
   <si>
@@ -423,6 +474,9 @@
     <t>全能骑士</t>
   </si>
   <si>
+    <t>10002004;10</t>
+  </si>
+  <si>
     <t>0;20000005@1;30000013@3;30000014@5;30000015</t>
   </si>
   <si>
@@ -432,6 +486,9 @@
     <t>冰女</t>
   </si>
   <si>
+    <t>10002005;10</t>
+  </si>
+  <si>
     <t>0;20000004@1;30000010@3;30000011@5;30000012</t>
   </si>
   <si>
@@ -439,6 +496,9 @@
   </si>
   <si>
     <t>术士</t>
+  </si>
+  <si>
+    <t>10002006;10</t>
   </si>
   <si>
     <t>0;20000006@1;30000016@3;30000017@5;30000018</t>
@@ -629,18 +689,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,6 +716,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,7 +1087,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1045,16 +1111,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1063,90 +1129,90 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,10 +1228,25 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1488,23 +1569,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="7" width="17.875" style="2"/>
-    <col min="8" max="8" width="27.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.875" style="2"/>
-    <col min="10" max="10" width="25.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="61.25" style="2" customWidth="1"/>
-    <col min="12" max="23" width="15.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="25.625" style="2" customWidth="1"/>
-    <col min="25" max="28" width="15.625" style="2" customWidth="1"/>
-    <col min="29" max="29" width="50.625" style="2" customWidth="1"/>
-    <col min="30" max="16384" width="17.875" style="2"/>
+    <col min="2" max="6" width="17.875" style="2"/>
+    <col min="7" max="7" width="35.625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="17.875" style="2"/>
+    <col min="10" max="10" width="27.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.875" style="2"/>
+    <col min="12" max="12" width="25.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="61.25" style="2" customWidth="1"/>
+    <col min="14" max="25" width="15.625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="25.625" style="2" customWidth="1"/>
+    <col min="27" max="30" width="15.625" style="2" customWidth="1"/>
+    <col min="31" max="31" width="50.625" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1603,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1592,191 +1675,209 @@
       <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="T3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="V3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="W3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="X3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="Y3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="Z3" s="6" t="s">
         <v>62</v>
       </c>
+      <c r="AA3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE3" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:29">
+    <row r="4" customHeight="1" spans="1:31">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1784,85 +1885,91 @@
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="2">
         <v>10001001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I4" s="2">
         <v>10001001</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" s="2">
+      <c r="L4" s="2">
         <v>10000001</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="2">
         <v>14000</v>
       </c>
-      <c r="M4" s="2">
+      <c r="O4" s="2">
         <v>60</v>
       </c>
-      <c r="N4" s="2">
+      <c r="P4" s="2">
         <v>60</v>
       </c>
-      <c r="O4" s="2">
+      <c r="Q4" s="2">
         <v>50</v>
       </c>
-      <c r="P4" s="2">
+      <c r="R4" s="2">
         <v>50</v>
       </c>
-      <c r="Q4" s="6">
-        <v>500</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="S4" s="10">
         <v>500</v>
       </c>
       <c r="T4" s="2">
         <v>0</v>
       </c>
       <c r="U4" s="2">
+        <v>500</v>
+      </c>
+      <c r="V4" s="2">
         <v>0</v>
       </c>
-      <c r="V4" s="2">
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2">
         <v>60000</v>
       </c>
-      <c r="W4" s="2">
+      <c r="Y4" s="2">
         <v>10000</v>
       </c>
-      <c r="X4" s="2">
+      <c r="Z4" s="2">
         <v>20000</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="AA4" s="2">
         <v>150</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="AB4" s="2">
         <v>10</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AC4" s="2">
         <v>20</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AD4" s="2">
         <v>20</v>
       </c>
-      <c r="AC4" s="2" t="s">
-        <v>66</v>
+      <c r="AE4" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:29">
+    <row r="5" customHeight="1" spans="1:31">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1870,44 +1977,44 @@
       <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="8">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="2">
         <v>10001002</v>
       </c>
-      <c r="G5" s="2">
+      <c r="I5" s="2">
         <v>10001002</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="2">
+      <c r="L5" s="2">
         <v>10000001</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="2">
         <v>8000</v>
       </c>
-      <c r="M5" s="2">
+      <c r="O5" s="2">
         <v>100</v>
       </c>
-      <c r="N5" s="2">
+      <c r="P5" s="2">
         <v>100</v>
       </c>
-      <c r="O5" s="2">
+      <c r="Q5" s="2">
         <v>30</v>
       </c>
-      <c r="P5" s="2">
+      <c r="R5" s="2">
         <v>30</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>500</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
       </c>
       <c r="S5" s="2">
         <v>500</v>
@@ -1916,39 +2023,45 @@
         <v>0</v>
       </c>
       <c r="U5" s="2">
+        <v>500</v>
+      </c>
+      <c r="V5" s="2">
         <v>0</v>
       </c>
-      <c r="V5" s="2">
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2">
         <v>60000</v>
       </c>
-      <c r="W5" s="2">
+      <c r="Y5" s="2">
         <v>10000</v>
       </c>
-      <c r="X5" s="2">
+      <c r="Z5" s="2">
         <v>20000</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="AA5" s="2">
         <v>100</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="AB5" s="2">
         <v>20</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AC5" s="2">
         <v>10</v>
       </c>
-      <c r="AB5" s="2">
+      <c r="AD5" s="2">
         <v>10</v>
       </c>
-      <c r="AC5" s="2" t="s">
-        <v>69</v>
+      <c r="AE5" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:29">
+    <row r="6" customHeight="1" spans="1:31">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1956,44 +2069,44 @@
       <c r="E6" s="2">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="8">
+        <v>3</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="2">
         <v>10001003</v>
       </c>
-      <c r="G6" s="2">
+      <c r="I6" s="2">
         <v>10001003</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <v>10000001</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="2">
         <v>8000</v>
       </c>
-      <c r="M6" s="2">
+      <c r="O6" s="2">
         <v>100</v>
       </c>
-      <c r="N6" s="2">
+      <c r="P6" s="2">
         <v>100</v>
       </c>
-      <c r="O6" s="2">
+      <c r="Q6" s="2">
         <v>30</v>
       </c>
-      <c r="P6" s="2">
+      <c r="R6" s="2">
         <v>30</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>500</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0</v>
       </c>
       <c r="S6" s="2">
         <v>500</v>
@@ -2002,39 +2115,45 @@
         <v>0</v>
       </c>
       <c r="U6" s="2">
+        <v>500</v>
+      </c>
+      <c r="V6" s="2">
         <v>0</v>
       </c>
-      <c r="V6" s="2">
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
         <v>60000</v>
       </c>
-      <c r="W6" s="2">
+      <c r="Y6" s="2">
         <v>10000</v>
       </c>
-      <c r="X6" s="2">
+      <c r="Z6" s="2">
         <v>20000</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="AA6" s="2">
         <v>100</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="AB6" s="2">
         <v>20</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AC6" s="2">
         <v>10</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AD6" s="2">
         <v>10</v>
       </c>
-      <c r="AC6" s="2" t="s">
-        <v>72</v>
+      <c r="AE6" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:29">
+    <row r="7" customHeight="1" spans="1:31">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2042,44 +2161,44 @@
       <c r="E7" s="2">
         <v>3</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="8">
+        <v>4</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="2">
         <v>10001004</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>10001004</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>10000001</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="2">
         <v>10000</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>80</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>80</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>40</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>40</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>500</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
       </c>
       <c r="S7" s="2">
         <v>500</v>
@@ -2088,39 +2207,45 @@
         <v>0</v>
       </c>
       <c r="U7" s="2">
+        <v>500</v>
+      </c>
+      <c r="V7" s="2">
         <v>0</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
         <v>60000</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>10000</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>20000</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>120</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>15</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>15</v>
       </c>
       <c r="AB7" s="2">
         <v>15</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>75</v>
+      <c r="AC7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:29">
+    <row r="8" customHeight="1" spans="1:31">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2128,44 +2253,44 @@
       <c r="E8" s="2">
         <v>2</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2">
         <v>10002001</v>
       </c>
-      <c r="G8" s="2">
+      <c r="I8" s="2">
         <v>10002001</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="J8" s="2">
+      <c r="L8" s="2">
         <v>10000002</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="2">
         <v>8000</v>
       </c>
-      <c r="M8" s="2">
+      <c r="O8" s="2">
         <v>100</v>
       </c>
-      <c r="N8" s="2">
+      <c r="P8" s="2">
         <v>100</v>
       </c>
-      <c r="O8" s="2">
+      <c r="Q8" s="2">
         <v>30</v>
       </c>
-      <c r="P8" s="2">
+      <c r="R8" s="2">
         <v>30</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>500</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
       </c>
       <c r="S8" s="2">
         <v>500</v>
@@ -2174,39 +2299,45 @@
         <v>0</v>
       </c>
       <c r="U8" s="2">
+        <v>500</v>
+      </c>
+      <c r="V8" s="2">
         <v>0</v>
       </c>
-      <c r="V8" s="2">
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
         <v>60000</v>
       </c>
-      <c r="W8" s="2">
+      <c r="Y8" s="2">
         <v>10000</v>
       </c>
-      <c r="X8" s="2">
+      <c r="Z8" s="2">
         <v>80000</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="AA8" s="2">
         <v>100</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="AB8" s="2">
         <v>20</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AC8" s="2">
         <v>10</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AD8" s="2">
         <v>10</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>78</v>
+      <c r="AE8" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:29">
+    <row r="9" customHeight="1" spans="1:31">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2214,77 +2345,83 @@
       <c r="E9" s="2">
         <v>3</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="11">
+        <v>6</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2">
         <v>10002002</v>
       </c>
-      <c r="G9" s="2">
+      <c r="I9" s="2">
         <v>10002002</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="2">
         <v>2</v>
       </c>
-      <c r="J9" s="2">
+      <c r="L9" s="2">
         <v>10000003</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O9" s="2">
         <v>80</v>
       </c>
-      <c r="L9" s="2">
-        <v>10000</v>
-      </c>
-      <c r="M9" s="2">
+      <c r="P9" s="2">
         <v>80</v>
       </c>
-      <c r="N9" s="2">
-        <v>80</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="Q9" s="2">
         <v>40</v>
       </c>
-      <c r="P9" s="2">
+      <c r="R9" s="2">
         <v>40</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="S9" s="10">
         <v>1000000</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>500</v>
       </c>
       <c r="T9" s="2">
         <v>0</v>
       </c>
       <c r="U9" s="2">
+        <v>500</v>
+      </c>
+      <c r="V9" s="2">
         <v>0</v>
       </c>
-      <c r="V9" s="2">
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
         <v>60000</v>
       </c>
-      <c r="W9" s="2">
+      <c r="Y9" s="2">
         <v>10000</v>
       </c>
-      <c r="X9" s="2">
+      <c r="Z9" s="2">
         <v>80000</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="AA9" s="2">
         <v>120</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>15</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>15</v>
       </c>
       <c r="AB9" s="2">
         <v>15</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>81</v>
+      <c r="AC9" s="2">
+        <v>15</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>15</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -221,12 +221,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="Z3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表SkillConfig
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -303,6 +326,9 @@
     <t>Base_AtkSpeed</t>
   </si>
   <si>
+    <t>Radius</t>
+  </si>
+  <si>
     <t>AtkDistance</t>
   </si>
   <si>
@@ -342,6 +368,9 @@
     <t>long</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -414,6 +443,9 @@
     <t>攻击速度</t>
   </si>
   <si>
+    <t>半径</t>
+  </si>
+  <si>
     <t>攻击距离</t>
   </si>
   <si>
@@ -442,6 +474,12 @@
   </si>
   <si>
     <t>0;20000001@1;30000001@3;30000002@5;30000003</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>30000</t>
   </si>
   <si>
     <t>一个拿着斧头的强壮家伙。</t>
@@ -1243,10 +1281,10 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1569,7 +1607,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1581,13 +1619,14 @@
     <col min="12" max="12" width="25.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="61.25" style="2" customWidth="1"/>
     <col min="14" max="25" width="15.625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="25.625" style="2" customWidth="1"/>
-    <col min="27" max="30" width="15.625" style="2" customWidth="1"/>
-    <col min="31" max="31" width="50.625" style="2" customWidth="1"/>
-    <col min="32" max="16384" width="17.875" style="2"/>
+    <col min="26" max="26" width="16" style="2" customWidth="1"/>
+    <col min="27" max="27" width="25.625" style="2" customWidth="1"/>
+    <col min="28" max="31" width="15.625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="50.625" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:31">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,203 +1720,212 @@
       <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:31">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE2" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="AF2" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:31">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:31">
+    <row r="4" customHeight="1" spans="2:32">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1889,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2">
         <v>10001001</v>
@@ -1898,7 +1946,7 @@
         <v>10001001</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -1907,7 +1955,7 @@
         <v>10000001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N4" s="2">
         <v>14000</v>
@@ -1924,7 +1972,7 @@
       <c r="R4" s="2">
         <v>50</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="11">
         <v>500</v>
       </c>
       <c r="T4" s="2">
@@ -1945,31 +1993,34 @@
       <c r="Y4" s="2">
         <v>10000</v>
       </c>
-      <c r="Z4" s="2">
-        <v>20000</v>
-      </c>
-      <c r="AA4" s="2">
+      <c r="Z4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB4" s="2">
         <v>150</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AC4" s="2">
         <v>10</v>
-      </c>
-      <c r="AC4" s="2">
-        <v>20</v>
       </c>
       <c r="AD4" s="2">
         <v>20</v>
       </c>
-      <c r="AE4" s="2" t="s">
-        <v>72</v>
+      <c r="AE4" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:31">
+    <row r="5" customHeight="1" spans="2:32">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1981,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H5" s="2">
         <v>10001002</v>
@@ -1990,7 +2041,7 @@
         <v>10001002</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -1999,7 +2050,7 @@
         <v>10000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N5" s="2">
         <v>8000</v>
@@ -2037,31 +2088,34 @@
       <c r="Y5" s="2">
         <v>10000</v>
       </c>
-      <c r="Z5" s="2">
-        <v>20000</v>
-      </c>
-      <c r="AA5" s="2">
+      <c r="Z5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB5" s="2">
         <v>100</v>
       </c>
-      <c r="AB5" s="2">
+      <c r="AC5" s="2">
         <v>20</v>
-      </c>
-      <c r="AC5" s="2">
-        <v>10</v>
       </c>
       <c r="AD5" s="2">
         <v>10</v>
       </c>
-      <c r="AE5" s="2" t="s">
-        <v>76</v>
+      <c r="AE5" s="2">
+        <v>10</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:31">
+    <row r="6" customHeight="1" spans="2:32">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -2073,7 +2127,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2">
         <v>10001003</v>
@@ -2082,7 +2136,7 @@
         <v>10001003</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -2091,7 +2145,7 @@
         <v>10000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N6" s="2">
         <v>8000</v>
@@ -2129,31 +2183,34 @@
       <c r="Y6" s="2">
         <v>10000</v>
       </c>
-      <c r="Z6" s="2">
-        <v>20000</v>
-      </c>
-      <c r="AA6" s="2">
+      <c r="Z6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB6" s="2">
         <v>100</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AC6" s="2">
         <v>20</v>
-      </c>
-      <c r="AC6" s="2">
-        <v>10</v>
       </c>
       <c r="AD6" s="2">
         <v>10</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>80</v>
+      <c r="AE6" s="2">
+        <v>10</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:31">
+    <row r="7" customHeight="1" spans="2:32">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2165,7 +2222,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2">
         <v>10001004</v>
@@ -2174,7 +2231,7 @@
         <v>10001004</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -2183,7 +2240,7 @@
         <v>10000001</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2">
         <v>10000</v>
@@ -2221,14 +2278,14 @@
       <c r="Y7" s="2">
         <v>10000</v>
       </c>
-      <c r="Z7" s="2">
-        <v>20000</v>
-      </c>
-      <c r="AA7" s="2">
+      <c r="Z7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="2">
         <v>120</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>15</v>
       </c>
       <c r="AC7" s="2">
         <v>15</v>
@@ -2236,16 +2293,19 @@
       <c r="AD7" s="2">
         <v>15</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>84</v>
+      <c r="AE7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:31">
+    <row r="8" customHeight="1" spans="2:32">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2257,7 +2317,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2">
         <v>10002001</v>
@@ -2266,7 +2326,7 @@
         <v>10002001</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
@@ -2275,7 +2335,7 @@
         <v>10000002</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="N8" s="2">
         <v>8000</v>
@@ -2313,31 +2373,34 @@
       <c r="Y8" s="2">
         <v>10000</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA8" s="2">
         <v>80000</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AB8" s="2">
         <v>100</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AC8" s="2">
         <v>20</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>10</v>
       </c>
       <c r="AD8" s="2">
         <v>10</v>
       </c>
-      <c r="AE8" s="2" t="s">
-        <v>88</v>
+      <c r="AE8" s="2">
+        <v>10</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:31">
+    <row r="9" customHeight="1" spans="2:32">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2345,11 +2408,11 @@
       <c r="E9" s="2">
         <v>3</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>6</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2">
         <v>10002002</v>
@@ -2358,7 +2421,7 @@
         <v>10002002</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K9" s="2">
         <v>2</v>
@@ -2367,7 +2430,7 @@
         <v>10000003</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N9" s="2">
         <v>10000</v>
@@ -2384,7 +2447,7 @@
       <c r="R9" s="2">
         <v>40</v>
       </c>
-      <c r="S9" s="10">
+      <c r="S9" s="11">
         <v>1000000</v>
       </c>
       <c r="T9" s="2">
@@ -2405,14 +2468,14 @@
       <c r="Y9" s="2">
         <v>10000</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA9" s="2">
         <v>80000</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AB9" s="2">
         <v>120</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>15</v>
       </c>
       <c r="AC9" s="2">
         <v>15</v>
@@ -2420,8 +2483,11 @@
       <c r="AD9" s="2">
         <v>15</v>
       </c>
-      <c r="AE9" s="2" t="s">
-        <v>92</v>
+      <c r="AE9" s="2">
+        <v>15</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -476,7 +476,7 @@
     <t>0;20000001@1;30000001@3;30000002@5;30000003</t>
   </si>
   <si>
-    <t>0.7</t>
+    <t>1</t>
   </si>
   <si>
     <t>30000</t>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -221,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="AA3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -290,6 +290,9 @@
     <t>UnlockSkillInfos</t>
   </si>
   <si>
+    <t>CenterY</t>
+  </si>
+  <si>
     <t>Base_Hp</t>
   </si>
   <si>
@@ -365,12 +368,12 @@
     <t>(array#sep=@),UnlockSkillInfo</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -407,6 +410,9 @@
     <t>英雄技能ID</t>
   </si>
   <si>
+    <t>中心位置</t>
+  </si>
+  <si>
     <t>血量</t>
   </si>
   <si>
@@ -474,6 +480,9 @@
   </si>
   <si>
     <t>0;20000001@1;30000001@3;30000002@5;30000003</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -1607,7 +1616,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1618,15 +1627,15 @@
     <col min="11" max="11" width="17.875" style="2"/>
     <col min="12" max="12" width="25.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="61.25" style="2" customWidth="1"/>
-    <col min="14" max="25" width="15.625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="16" style="2" customWidth="1"/>
-    <col min="27" max="27" width="25.625" style="2" customWidth="1"/>
-    <col min="28" max="31" width="15.625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="50.625" style="2" customWidth="1"/>
-    <col min="33" max="16384" width="17.875" style="2"/>
+    <col min="14" max="26" width="15.625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="16" style="2" customWidth="1"/>
+    <col min="28" max="28" width="25.625" style="2" customWidth="1"/>
+    <col min="29" max="32" width="15.625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="50.625" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,209 +1732,218 @@
       <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="AB2" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF2" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="AG2" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF3" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="AG3" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:32">
+    <row r="4" customHeight="1" spans="2:33">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1937,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2">
         <v>10001001</v>
@@ -1946,7 +1964,7 @@
         <v>10001001</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -1955,72 +1973,75 @@
         <v>10000001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4" s="2">
+        <v>76</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="2">
         <v>14000</v>
-      </c>
-      <c r="O4" s="2">
-        <v>60</v>
       </c>
       <c r="P4" s="2">
         <v>60</v>
       </c>
       <c r="Q4" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R4" s="2">
         <v>50</v>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="2">
+        <v>50</v>
+      </c>
+      <c r="T4" s="11">
         <v>500</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>0</v>
       </c>
-      <c r="U4" s="2">
+      <c r="V4" s="2">
         <v>500</v>
-      </c>
-      <c r="V4" s="2">
-        <v>0</v>
       </c>
       <c r="W4" s="2">
         <v>0</v>
       </c>
       <c r="X4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2">
         <v>60000</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Z4" s="2">
         <v>10000</v>
       </c>
-      <c r="Z4" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="AA4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB4" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" s="2">
         <v>150</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AD4" s="2">
         <v>10</v>
-      </c>
-      <c r="AD4" s="2">
-        <v>20</v>
       </c>
       <c r="AE4" s="2">
         <v>20</v>
       </c>
-      <c r="AF4" s="2" t="s">
-        <v>77</v>
+      <c r="AF4" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:32">
+    <row r="5" customHeight="1" spans="2:33">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -2032,7 +2053,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2">
         <v>10001002</v>
@@ -2041,7 +2062,7 @@
         <v>10001002</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -2050,72 +2071,75 @@
         <v>10000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5" s="2">
+        <v>83</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="2">
         <v>8000</v>
-      </c>
-      <c r="O5" s="2">
-        <v>100</v>
       </c>
       <c r="P5" s="2">
         <v>100</v>
       </c>
       <c r="Q5" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="R5" s="2">
         <v>30</v>
       </c>
       <c r="S5" s="2">
+        <v>30</v>
+      </c>
+      <c r="T5" s="2">
         <v>500</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>0</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>500</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0</v>
       </c>
       <c r="W5" s="2">
         <v>0</v>
       </c>
       <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2">
         <v>60000</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Z5" s="2">
         <v>10000</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="AA5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB5" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC5" s="2">
         <v>100</v>
       </c>
-      <c r="AC5" s="2">
+      <c r="AD5" s="2">
         <v>20</v>
-      </c>
-      <c r="AD5" s="2">
-        <v>10</v>
       </c>
       <c r="AE5" s="2">
         <v>10</v>
       </c>
-      <c r="AF5" s="2" t="s">
-        <v>81</v>
+      <c r="AF5" s="2">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:32">
+    <row r="6" customHeight="1" spans="2:33">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -2127,7 +2151,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2">
         <v>10001003</v>
@@ -2136,7 +2160,7 @@
         <v>10001003</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -2145,72 +2169,75 @@
         <v>10000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="2">
+        <v>87</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="2">
         <v>8000</v>
-      </c>
-      <c r="O6" s="2">
-        <v>100</v>
       </c>
       <c r="P6" s="2">
         <v>100</v>
       </c>
       <c r="Q6" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="R6" s="2">
         <v>30</v>
       </c>
       <c r="S6" s="2">
+        <v>30</v>
+      </c>
+      <c r="T6" s="2">
         <v>500</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>0</v>
       </c>
-      <c r="U6" s="2">
+      <c r="V6" s="2">
         <v>500</v>
-      </c>
-      <c r="V6" s="2">
-        <v>0</v>
       </c>
       <c r="W6" s="2">
         <v>0</v>
       </c>
       <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
         <v>60000</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Z6" s="2">
         <v>10000</v>
       </c>
-      <c r="Z6" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="AA6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB6" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC6" s="2">
         <v>100</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AD6" s="2">
         <v>20</v>
-      </c>
-      <c r="AD6" s="2">
-        <v>10</v>
       </c>
       <c r="AE6" s="2">
         <v>10</v>
       </c>
-      <c r="AF6" s="2" t="s">
-        <v>85</v>
+      <c r="AF6" s="2">
+        <v>10</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:32">
+    <row r="7" customHeight="1" spans="2:33">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2222,7 +2249,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2">
         <v>10001004</v>
@@ -2231,7 +2258,7 @@
         <v>10001004</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -2240,55 +2267,55 @@
         <v>10000001</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="2">
+        <v>91</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="2">
         <v>10000</v>
-      </c>
-      <c r="O7" s="2">
-        <v>80</v>
       </c>
       <c r="P7" s="2">
         <v>80</v>
       </c>
       <c r="Q7" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R7" s="2">
         <v>40</v>
       </c>
       <c r="S7" s="2">
+        <v>40</v>
+      </c>
+      <c r="T7" s="2">
         <v>500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>0</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>500</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0</v>
       </c>
       <c r="W7" s="2">
         <v>0</v>
       </c>
       <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
         <v>60000</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>10000</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="AA7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB7" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" s="2">
         <v>120</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>15</v>
       </c>
       <c r="AD7" s="2">
         <v>15</v>
@@ -2296,16 +2323,19 @@
       <c r="AE7" s="2">
         <v>15</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>89</v>
+      <c r="AF7" s="2">
+        <v>15</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:32">
+    <row r="8" customHeight="1" spans="2:33">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2317,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2">
         <v>10002001</v>
@@ -2326,7 +2356,7 @@
         <v>10002001</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
@@ -2335,72 +2365,75 @@
         <v>10000002</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="2">
+        <v>95</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="2">
         <v>8000</v>
-      </c>
-      <c r="O8" s="2">
-        <v>100</v>
       </c>
       <c r="P8" s="2">
         <v>100</v>
       </c>
       <c r="Q8" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="R8" s="2">
         <v>30</v>
       </c>
       <c r="S8" s="2">
+        <v>30</v>
+      </c>
+      <c r="T8" s="2">
         <v>500</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>0</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>500</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
       </c>
       <c r="W8" s="2">
         <v>0</v>
       </c>
       <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
         <v>60000</v>
       </c>
-      <c r="Y8" s="2">
+      <c r="Z8" s="2">
         <v>10000</v>
       </c>
-      <c r="Z8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB8" s="2">
         <v>80000</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AC8" s="2">
         <v>100</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AD8" s="2">
         <v>20</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>10</v>
       </c>
       <c r="AE8" s="2">
         <v>10</v>
       </c>
-      <c r="AF8" s="2" t="s">
-        <v>93</v>
+      <c r="AF8" s="2">
+        <v>10</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:32">
+    <row r="9" customHeight="1" spans="2:33">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2412,7 +2445,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2">
         <v>10002002</v>
@@ -2421,7 +2454,7 @@
         <v>10002002</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K9" s="2">
         <v>2</v>
@@ -2430,55 +2463,55 @@
         <v>10000003</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N9" s="2">
+        <v>99</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="2">
         <v>10000</v>
-      </c>
-      <c r="O9" s="2">
-        <v>80</v>
       </c>
       <c r="P9" s="2">
         <v>80</v>
       </c>
       <c r="Q9" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R9" s="2">
         <v>40</v>
       </c>
-      <c r="S9" s="11">
+      <c r="S9" s="2">
+        <v>40</v>
+      </c>
+      <c r="T9" s="11">
         <v>1000000</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>0</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>500</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
       </c>
       <c r="W9" s="2">
         <v>0</v>
       </c>
       <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
         <v>60000</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Z9" s="2">
         <v>10000</v>
       </c>
-      <c r="Z9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB9" s="2">
         <v>80000</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AC9" s="2">
         <v>120</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>15</v>
       </c>
       <c r="AD9" s="2">
         <v>15</v>
@@ -2486,8 +2519,11 @@
       <c r="AE9" s="2">
         <v>15</v>
       </c>
-      <c r="AF9" s="2" t="s">
-        <v>97</v>
+      <c r="AF9" s="2">
+        <v>15</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="104">
   <si>
     <t>##var</t>
   </si>
@@ -485,6 +485,9 @@
     <t>2</t>
   </si>
   <si>
+    <t>50000</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -527,6 +530,9 @@
     <t>0;20000005@1;30000013@3;30000014@5;30000015</t>
   </si>
   <si>
+    <t>70000</t>
+  </si>
+  <si>
     <t>一个打辅助的骑士。</t>
   </si>
   <si>
@@ -537,6 +543,9 @@
   </si>
   <si>
     <t>0;20000004@1;30000010@3;30000011@5;30000012</t>
+  </si>
+  <si>
+    <t>40000</t>
   </si>
   <si>
     <t>冰冷的法师。</t>
@@ -2008,17 +2017,17 @@
       <c r="X4" s="2">
         <v>0</v>
       </c>
-      <c r="Y4" s="2">
-        <v>60000</v>
+      <c r="Y4" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="Z4" s="2">
         <v>10000</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" s="2">
         <v>150</v>
@@ -2033,7 +2042,7 @@
         <v>20</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:33">
@@ -2041,7 +2050,7 @@
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -2053,7 +2062,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2">
         <v>10001002</v>
@@ -2071,7 +2080,7 @@
         <v>10000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>77</v>
@@ -2106,17 +2115,17 @@
       <c r="X5" s="2">
         <v>0</v>
       </c>
-      <c r="Y5" s="2">
-        <v>60000</v>
+      <c r="Y5" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="Z5" s="2">
         <v>10000</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" s="2">
         <v>100</v>
@@ -2131,7 +2140,7 @@
         <v>10</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:33">
@@ -2139,7 +2148,7 @@
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -2151,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" s="2">
         <v>10001003</v>
@@ -2169,7 +2178,7 @@
         <v>10000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>77</v>
@@ -2211,10 +2220,10 @@
         <v>10000</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC6" s="2">
         <v>100</v>
@@ -2229,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:33">
@@ -2237,7 +2246,7 @@
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2249,7 +2258,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2">
         <v>10001004</v>
@@ -2267,7 +2276,7 @@
         <v>10000001</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>77</v>
@@ -2302,17 +2311,17 @@
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="2">
-        <v>60000</v>
+      <c r="Y7" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="Z7" s="2">
         <v>10000</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" s="2">
         <v>120</v>
@@ -2327,7 +2336,7 @@
         <v>15</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:33">
@@ -2335,7 +2344,7 @@
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2347,7 +2356,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2">
         <v>10002001</v>
@@ -2365,7 +2374,7 @@
         <v>10000002</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>77</v>
@@ -2400,14 +2409,14 @@
       <c r="X8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="2">
-        <v>60000</v>
+      <c r="Y8" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="Z8" s="2">
         <v>10000</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB8" s="2">
         <v>80000</v>
@@ -2425,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:33">
@@ -2433,7 +2442,7 @@
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2445,7 +2454,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H9" s="2">
         <v>10002002</v>
@@ -2463,7 +2472,7 @@
         <v>10000003</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>77</v>
@@ -2498,14 +2507,14 @@
       <c r="X9" s="2">
         <v>0</v>
       </c>
-      <c r="Y9" s="2">
-        <v>60000</v>
+      <c r="Y9" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="Z9" s="2">
         <v>10000</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB9" s="2">
         <v>80000</v>
@@ -2523,7 +2532,7 @@
         <v>15</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/HeroConfig.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig.xlsx
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -347,6 +347,9 @@
     <t>Lv_Adf</t>
   </si>
   <si>
+    <t>MaxAnger</t>
+  </si>
+  <si>
     <t>HeroDescription</t>
   </si>
   <si>
@@ -467,6 +470,9 @@
     <t>等级成长魔防</t>
   </si>
   <si>
+    <t>怒气</t>
+  </si>
+  <si>
     <t>英雄简介</t>
   </si>
   <si>
@@ -492,6 +498,9 @@
   </si>
   <si>
     <t>30000</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>一个拿着斧头的强壮家伙。</t>
@@ -745,12 +754,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1625,7 +1634,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1639,12 +1648,12 @@
     <col min="14" max="26" width="15.625" style="2" customWidth="1"/>
     <col min="27" max="27" width="16" style="2" customWidth="1"/>
     <col min="28" max="28" width="25.625" style="2" customWidth="1"/>
-    <col min="29" max="32" width="15.625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="50.625" style="2" customWidth="1"/>
-    <col min="34" max="16384" width="17.875" style="2"/>
+    <col min="29" max="33" width="15.625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="50.625" style="2" customWidth="1"/>
+    <col min="35" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1744,215 +1753,224 @@
       <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:34">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="AB2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AG2" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="AH2" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:34">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AF3" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AG3" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:33">
+    <row r="4" customHeight="1" spans="2:34">
       <c r="B4" s="2">
         <v>10001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1964,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2">
         <v>10001001</v>
@@ -1973,7 +1991,7 @@
         <v>10001001</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -1982,10 +2000,10 @@
         <v>10000001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O4" s="2">
         <v>14000</v>
@@ -2018,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z4" s="2">
         <v>10000</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC4" s="2">
         <v>150</v>
@@ -2042,15 +2060,18 @@
         <v>20</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:33">
+    <row r="5" customHeight="1" spans="2:34">
       <c r="B5" s="2">
         <v>10001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -2062,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2">
         <v>10001002</v>
@@ -2071,7 +2092,7 @@
         <v>10001002</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -2080,10 +2101,10 @@
         <v>10000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O5" s="2">
         <v>8000</v>
@@ -2116,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z5" s="2">
         <v>10000</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC5" s="2">
         <v>100</v>
@@ -2140,15 +2161,18 @@
         <v>10</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:33">
+    <row r="6" customHeight="1" spans="2:34">
       <c r="B6" s="2">
         <v>10001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -2160,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2">
         <v>10001003</v>
@@ -2169,7 +2193,7 @@
         <v>10001003</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -2178,10 +2202,10 @@
         <v>10000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2">
         <v>8000</v>
@@ -2220,10 +2244,10 @@
         <v>10000</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC6" s="2">
         <v>100</v>
@@ -2238,15 +2262,18 @@
         <v>10</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:33">
+    <row r="7" customHeight="1" spans="2:34">
       <c r="B7" s="2">
         <v>10001004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -2258,7 +2285,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
         <v>10001004</v>
@@ -2267,7 +2294,7 @@
         <v>10001004</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -2276,10 +2303,10 @@
         <v>10000001</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O7" s="2">
         <v>10000</v>
@@ -2312,16 +2339,16 @@
         <v>0</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Z7" s="2">
         <v>10000</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC7" s="2">
         <v>120</v>
@@ -2336,15 +2363,18 @@
         <v>15</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:33">
+    <row r="8" customHeight="1" spans="2:34">
       <c r="B8" s="2">
         <v>10002001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -2356,7 +2386,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2">
         <v>10002001</v>
@@ -2365,7 +2395,7 @@
         <v>10002001</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
@@ -2374,10 +2404,10 @@
         <v>10000002</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O8" s="2">
         <v>8000</v>
@@ -2410,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z8" s="2">
         <v>10000</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB8" s="2">
         <v>80000</v>
@@ -2434,15 +2464,18 @@
         <v>10</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:33">
+    <row r="9" customHeight="1" spans="2:34">
       <c r="B9" s="2">
         <v>10002002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -2454,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2">
         <v>10002002</v>
@@ -2463,7 +2496,7 @@
         <v>10002002</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K9" s="2">
         <v>2</v>
@@ -2472,10 +2505,10 @@
         <v>10000003</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O9" s="2">
         <v>10000</v>
@@ -2508,13 +2541,13 @@
         <v>0</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z9" s="2">
         <v>10000</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AB9" s="2">
         <v>80000</v>
@@ -2532,7 +2565,10 @@
         <v>15</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
